--- a/Result/profitability/6229.xlsx
+++ b/Result/profitability/6229.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0325</v>
+        <v>0.09375</v>
       </c>
       <c r="N2" t="n">
-        <v>11.315</v>
+        <v>10.84625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.29</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05374999999999999</v>
+        <v>0.12375</v>
       </c>
       <c r="N3" t="n">
-        <v>11.64875</v>
+        <v>11.51375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -801,7 +801,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.62</v>
       </c>
       <c r="M4" t="n">
-        <v>0.125</v>
+        <v>0.18875</v>
       </c>
       <c r="N4" t="n">
-        <v>12.28625</v>
+        <v>12.1025</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.02</v>
       </c>
       <c r="M5" t="n">
-        <v>0.11</v>
+        <v>0.23375</v>
       </c>
       <c r="N5" t="n">
-        <v>12.2475</v>
+        <v>12.13</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>0.14375</v>
+        <v>0.1875</v>
       </c>
       <c r="N6" t="n">
-        <v>12.13</v>
+        <v>11.975</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.19</v>
       </c>
       <c r="M7" t="n">
-        <v>0.135</v>
+        <v>0.2025</v>
       </c>
       <c r="N7" t="n">
-        <v>12.02625</v>
+        <v>12.00875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.26</v>
       </c>
       <c r="M8" t="n">
-        <v>0.15875</v>
+        <v>0.2175</v>
       </c>
       <c r="N8" t="n">
-        <v>12.02</v>
+        <v>12.1025</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6229</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>819</v>
+      </c>
+      <c r="D75" t="n">
+        <v>740</v>
+      </c>
+      <c r="E75" t="n">
+        <v>80</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="G75" t="n">
+        <v>20</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.40%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>12</v>
+      </c>
+      <c r="J75" t="n">
+        <v>32</v>
+      </c>
+      <c r="K75" t="n">
+        <v>25</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.12125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>10.725</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="X75" t="n">
+        <v>3.357142857142857</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.6600000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.07276736493936053</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.605263157894737</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.9399999999999995</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.08809746954076847</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
